--- a/resources/reselling/files/reselling-int-floor-card.xlsx
+++ b/resources/reselling/files/reselling-int-floor-card.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,11 +67,6 @@
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="4">
     <fill>
@@ -117,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,8 +145,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="74" customWidth="1" min="1" max="1"/>
@@ -551,7 +544,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Postage (your real mailer, priced in)</t>
+          <t>Shipping (your real mailer, priced in)</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
@@ -879,7 +872,7 @@
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>Defaults checked 10 October 2026: eBay 13.6% of the whole order including sales tax, plus $0.40 per order over $10 ($0.30 at $10 or less); Mercari 10% of item + any buyer-paid shipping, no processing or per-order fee. Fees change — read the platform's own fee page and update the yellow cells. Pay-per-click promotion can't go in this formula; budget it separately.</t>
+          <t>Defaults checked October 10, 2026: eBay 13.6% of the whole order including sales tax, plus $0.40 per order over $10 ($0.30 at $10 or less); Mercari 10% of item + any buyer-paid shipping, no processing or per-order fee. Fees change — read the platform's own fee page and update the yellow cells. Pay-per-click promotion can't go in this formula; budget it separately.</t>
         </is>
       </c>
     </row>
@@ -890,10 +883,6 @@
           <t>ePORTS — your ecom source. eports.global  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
         </is>
       </c>
-    </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" s="15" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/reselling/files/reselling-int-floor-card.xlsx
+++ b/resources/reselling/files/reselling-int-floor-card.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -140,9 +140,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -513,14 +510,14 @@
   <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="74" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Floor card — twelve floors in two minutes (Reselling — Intermediate, ch6/9)</t>
         </is>
@@ -533,7 +530,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -591,7 +587,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" ht="33" customHeight="1">
+    <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Fixed total (before any per-order fee)</t>
@@ -602,8 +598,7 @@
         <v/>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12" ht="48" customHeight="1">
+    <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Platform settings</t>
@@ -685,7 +680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="33" customHeight="1">
+    <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Planning rate (rounded UP to the whole %)</t>
@@ -715,7 +710,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="48" customHeight="1">
+    <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>Formula check</t>
@@ -730,8 +725,7 @@
         <v/>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22" ht="33" customHeight="1">
+    <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
           <t>Cost you paid</t>
@@ -820,7 +814,6 @@
         </is>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
@@ -831,7 +824,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="31" ht="48" customHeight="1">
+    <row r="31">
       <c r="A31" t="inlineStr">
         <is>
           <t>Max buy (rounded DOWN to the dollar on the route)</t>
@@ -846,7 +839,6 @@
         <v/>
       </c>
     </row>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
@@ -868,7 +860,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
@@ -876,11 +867,10 @@
         </is>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
+          <t>ePORTS — your ecom source (eports.global)  ·  The Reselling shelf: Basics · Intermediate · Advanced — eports.global/resources/reselling</t>
         </is>
       </c>
     </row>
